--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_individual_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755175568_individual_h_10.xlsx
@@ -658,7 +658,7 @@
         <v>0.008508942972900661</v>
       </c>
       <c r="C2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>44227973</v>
+        <v>4159635</v>
       </c>
       <c r="L2" t="n">
-        <v>23500082</v>
+        <v>1622976</v>
       </c>
       <c r="M2" t="n">
-        <v>5549671</v>
+        <v>328578</v>
       </c>
       <c r="N2" t="n">
-        <v>238386</v>
+        <v>7343</v>
       </c>
       <c r="O2" t="n">
-        <v>3304432</v>
+        <v>199304</v>
       </c>
       <c r="P2" t="n">
-        <v>1240135</v>
+        <v>60958</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999758005142212</v>
+        <v>0.9999856352806091</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8439558744430542</v>
+        <v>0.7226507663726807</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7212504148483276</v>
+        <v>0.5577421188354492</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6506413221359253</v>
+        <v>0.4279786050319672</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2622029483318329</v>
+        <v>0.0638449564576149</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6970094442367554</v>
+        <v>0.4714598655700684</v>
       </c>
       <c r="W2" t="n">
-        <v>0.812073826789856</v>
+        <v>0.6216968894004822</v>
       </c>
       <c r="X2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>63463800</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="AG2" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AH2" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AI2" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560742974281311</v>
+        <v>0.9549785256385803</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911531388759613</v>
+        <v>0.912082850933075</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580335974693298</v>
+        <v>0.8579939603805542</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661676824092865</v>
+        <v>0.6605360507965088</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019646048545837</v>
+        <v>0.90191650390625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002036865544291333</v>
       </c>
       <c r="C3" t="n">
-        <v>967</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>44227973</v>
+        <v>4159635</v>
       </c>
       <c r="E3" t="n">
-        <v>6024978</v>
+        <v>798639</v>
       </c>
       <c r="F3" t="n">
-        <v>167036</v>
+        <v>38469</v>
       </c>
       <c r="G3" t="n">
-        <v>13457</v>
+        <v>2975</v>
       </c>
       <c r="H3" t="n">
-        <v>10816</v>
+        <v>2989</v>
       </c>
       <c r="I3" t="n">
-        <v>636</v>
+        <v>267</v>
       </c>
       <c r="J3" t="n">
-        <v>100694666</v>
+        <v>10069529</v>
       </c>
       <c r="K3" t="n">
-        <v>105536559</v>
+        <v>9816566</v>
       </c>
       <c r="L3" t="n">
-        <v>122124345</v>
+        <v>11800687</v>
       </c>
       <c r="M3" t="n">
-        <v>151814656</v>
+        <v>15034310</v>
       </c>
       <c r="N3" t="n">
-        <v>162593872</v>
+        <v>16218352</v>
       </c>
       <c r="O3" t="n">
-        <v>157621980</v>
+        <v>15680628</v>
       </c>
       <c r="P3" t="n">
-        <v>161938401</v>
+        <v>16185102</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.876741349697113</v>
+        <v>0.8314297795295715</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7131324410438538</v>
+        <v>0.4876166582107544</v>
       </c>
       <c r="T3" t="n">
-        <v>0.592566967010498</v>
+        <v>0.3486149907112122</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2662495374679565</v>
+        <v>0.0816088393330574</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6477270722389221</v>
+        <v>0.3893127739429474</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6410248279571533</v>
+        <v>0.3145326375961304</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>48303112</v>
+        <v>4789433</v>
       </c>
       <c r="Z3" t="n">
-        <v>1988133</v>
+        <v>198166</v>
       </c>
       <c r="AA3" t="n">
-        <v>85525</v>
+        <v>8476</v>
       </c>
       <c r="AB3" t="n">
-        <v>68445</v>
+        <v>6874</v>
       </c>
       <c r="AC3" t="n">
-        <v>348</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>100696200</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>111494909</v>
+        <v>11187217</v>
       </c>
       <c r="AG3" t="n">
-        <v>128296811</v>
+        <v>12795836</v>
       </c>
       <c r="AH3" t="n">
-        <v>153466369</v>
+        <v>15339900</v>
       </c>
       <c r="AI3" t="n">
-        <v>162962027</v>
+        <v>16295512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>158558602</v>
+        <v>15853902</v>
       </c>
       <c r="AK3" t="n">
-        <v>162092809</v>
+        <v>16208926</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575237631797791</v>
+        <v>0.957314133644104</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098227620124817</v>
+        <v>0.9094545841217041</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8571126461029053</v>
+        <v>0.8562752604484558</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6610390543937683</v>
+        <v>0.6597946286201477</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013901948928833</v>
+        <v>0.900970458984375</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03212849016620213</v>
       </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>7578778</v>
+        <v>1439019</v>
       </c>
       <c r="E4" t="n">
-        <v>23500082</v>
+        <v>1622976</v>
       </c>
       <c r="F4" t="n">
-        <v>1602275</v>
+        <v>210852</v>
       </c>
       <c r="G4" t="n">
-        <v>85321</v>
+        <v>17197</v>
       </c>
       <c r="H4" t="n">
-        <v>171468</v>
+        <v>34910</v>
       </c>
       <c r="I4" t="n">
-        <v>15344</v>
+        <v>3414</v>
       </c>
       <c r="J4" t="n">
-        <v>1534</v>
+        <v>91</v>
       </c>
       <c r="K4" t="n">
-        <v>8177578</v>
+        <v>1596444</v>
       </c>
       <c r="L4" t="n">
-        <v>9082335</v>
+        <v>1286928</v>
       </c>
       <c r="M4" t="n">
-        <v>2979869</v>
+        <v>439166</v>
       </c>
       <c r="N4" t="n">
-        <v>670780</v>
+        <v>107670</v>
       </c>
       <c r="O4" t="n">
-        <v>1436439</v>
+        <v>223434</v>
       </c>
       <c r="P4" t="n">
-        <v>286986</v>
+        <v>37093</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999879002571106</v>
+        <v>0.9999927878379822</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8600362539291382</v>
+        <v>0.7732332348823547</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7171684503555298</v>
+        <v>0.5203272700309753</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6202477216720581</v>
+        <v>0.3842415511608124</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2642107307910919</v>
+        <v>0.07164217531681061</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6714651584625244</v>
+        <v>0.4264665246009827</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7164819836616516</v>
+        <v>0.4177265465259552</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2072431</v>
+        <v>211003</v>
       </c>
       <c r="Z4" t="n">
-        <v>29981680</v>
+        <v>3027015</v>
       </c>
       <c r="AA4" t="n">
-        <v>831668</v>
+        <v>83549</v>
       </c>
       <c r="AB4" t="n">
-        <v>55444</v>
+        <v>5619</v>
       </c>
       <c r="AC4" t="n">
-        <v>11417</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2219228</v>
+        <v>225793</v>
       </c>
       <c r="AG4" t="n">
-        <v>2909869</v>
+        <v>291779</v>
       </c>
       <c r="AH4" t="n">
-        <v>1328156</v>
+        <v>133576</v>
       </c>
       <c r="AI4" t="n">
-        <v>302625</v>
+        <v>30510</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499817</v>
+        <v>50160</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567984938621521</v>
+        <v>0.9561448693275452</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106762409210205</v>
+        <v>0.9107667803764343</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575728535652161</v>
+        <v>0.8571337461471558</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6613578200340271</v>
+        <v>0.6601651310920715</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016773700714111</v>
+        <v>0.9014432430267334</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>425414</v>
+        <v>117424</v>
       </c>
       <c r="E5" t="n">
-        <v>2507643</v>
+        <v>373293</v>
       </c>
       <c r="F5" t="n">
-        <v>5549671</v>
+        <v>328578</v>
       </c>
       <c r="G5" t="n">
-        <v>218553</v>
+        <v>31637</v>
       </c>
       <c r="H5" t="n">
-        <v>604562</v>
+        <v>81232</v>
       </c>
       <c r="I5" t="n">
-        <v>59444</v>
+        <v>10350</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6217890</v>
+        <v>843355</v>
       </c>
       <c r="L5" t="n">
-        <v>9453238</v>
+        <v>1705409</v>
       </c>
       <c r="M5" t="n">
-        <v>3815804</v>
+        <v>613946</v>
       </c>
       <c r="N5" t="n">
-        <v>656962</v>
+        <v>82635</v>
       </c>
       <c r="O5" t="n">
-        <v>1797149</v>
+        <v>312634</v>
       </c>
       <c r="P5" t="n">
-        <v>694478</v>
+        <v>132847</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999906420707703</v>
+        <v>0.9999944567680359</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9123083353042603</v>
+        <v>0.8513767719268799</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8870883584022522</v>
+        <v>0.8177182674407959</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9586033821105957</v>
+        <v>0.9358484148979187</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9919118881225586</v>
+        <v>0.9884073734283447</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9803022146224976</v>
+        <v>0.9673447608947754</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9940212965011597</v>
+        <v>0.9896479249000549</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80954</v>
+        <v>8141</v>
       </c>
       <c r="Z5" t="n">
-        <v>859027</v>
+        <v>87332</v>
       </c>
       <c r="AA5" t="n">
-        <v>8027267</v>
+        <v>807060</v>
       </c>
       <c r="AB5" t="n">
-        <v>99883</v>
+        <v>10049</v>
       </c>
       <c r="AC5" t="n">
-        <v>292014</v>
+        <v>29309</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2142751</v>
+        <v>213557</v>
       </c>
       <c r="AG5" t="n">
-        <v>2971640</v>
+        <v>301370</v>
       </c>
       <c r="AH5" t="n">
-        <v>1338208</v>
+        <v>135464</v>
       </c>
       <c r="AI5" t="n">
-        <v>303488</v>
+        <v>30611</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503066</v>
+        <v>50697</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97342848777771</v>
+        <v>0.9732365012168884</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641720652580261</v>
+        <v>0.9638676047325134</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837575554847717</v>
+        <v>0.9836111068725586</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963077902793884</v>
+        <v>0.9962767362594604</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938908219337463</v>
+        <v>0.9938561916351318</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998381495475769</v>
+        <v>0.9983761310577393</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>127</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>136884</v>
+        <v>23414</v>
       </c>
       <c r="E6" t="n">
-        <v>189748</v>
+        <v>23787</v>
       </c>
       <c r="F6" t="n">
-        <v>228834</v>
+        <v>24914</v>
       </c>
       <c r="G6" t="n">
-        <v>238386</v>
+        <v>7343</v>
       </c>
       <c r="H6" t="n">
-        <v>92851</v>
+        <v>9422</v>
       </c>
       <c r="I6" t="n">
-        <v>8518</v>
+        <v>1085</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>65324</v>
+        <v>6613</v>
       </c>
       <c r="Z6" t="n">
-        <v>53793</v>
+        <v>5390</v>
       </c>
       <c r="AA6" t="n">
-        <v>109579</v>
+        <v>11097</v>
       </c>
       <c r="AB6" t="n">
-        <v>591860</v>
+        <v>59367</v>
       </c>
       <c r="AC6" t="n">
-        <v>69982</v>
+        <v>7030</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>34771</v>
+        <v>15536</v>
       </c>
       <c r="E7" t="n">
-        <v>330432</v>
+        <v>82066</v>
       </c>
       <c r="F7" t="n">
-        <v>910160</v>
+        <v>145862</v>
       </c>
       <c r="G7" t="n">
-        <v>318696</v>
+        <v>47171</v>
       </c>
       <c r="H7" t="n">
-        <v>3304432</v>
+        <v>199304</v>
       </c>
       <c r="I7" t="n">
-        <v>203044</v>
+        <v>21977</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8106</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>298070</v>
+        <v>30121</v>
       </c>
       <c r="AB7" t="n">
-        <v>76193</v>
+        <v>7701</v>
       </c>
       <c r="AC7" t="n">
-        <v>4598515</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>1731</v>
+        <v>1051</v>
       </c>
       <c r="E8" t="n">
-        <v>29534</v>
+        <v>9143</v>
       </c>
       <c r="F8" t="n">
-        <v>71564</v>
+        <v>19069</v>
       </c>
       <c r="G8" t="n">
-        <v>34753</v>
+        <v>8690</v>
       </c>
       <c r="H8" t="n">
-        <v>556742</v>
+        <v>94881</v>
       </c>
       <c r="I8" t="n">
-        <v>1240135</v>
+        <v>60958</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
